--- a/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0003T0006Z000C1N12_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0003T0006Z000C1N12_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.61516758750177</v>
+        <v>3.999964732969038</v>
       </c>
       <c r="D2" t="n">
-        <v>23.13547060251855</v>
+        <v>3.759513972909264</v>
       </c>
       <c r="E2" t="n">
-        <v>22.0040899680784</v>
+        <v>3.57566461981274</v>
       </c>
       <c r="F2" t="n">
-        <v>25.44277870537601</v>
+        <v>4.134451539623601</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.8948719268048</v>
+        <v>3.232916688105779</v>
       </c>
       <c r="D3" t="n">
-        <v>9.409476846110682</v>
+        <v>1.529039987492986</v>
       </c>
       <c r="E3" t="n">
-        <v>22.0040899680784</v>
+        <v>3.57566461981274</v>
       </c>
       <c r="F3" t="n">
-        <v>25.44277870537601</v>
+        <v>4.134451539623601</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>44.95635005250494</v>
+        <v>7.305406883532053</v>
       </c>
       <c r="D4" t="n">
-        <v>16.53804536347765</v>
+        <v>2.687432371565118</v>
       </c>
       <c r="E4" t="n">
-        <v>22.0040899680784</v>
+        <v>3.57566461981274</v>
       </c>
       <c r="F4" t="n">
-        <v>25.44277870537601</v>
+        <v>4.134451539623601</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>10.23340231901466</v>
+        <v>1.662927876839882</v>
       </c>
       <c r="D5" t="n">
-        <v>12.80986907186018</v>
+        <v>2.081603724177279</v>
       </c>
       <c r="E5" t="n">
-        <v>22.0040899680784</v>
+        <v>3.57566461981274</v>
       </c>
       <c r="F5" t="n">
-        <v>25.44277870537601</v>
+        <v>4.134451539623601</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>23.93819555482835</v>
+        <v>3.889956777659607</v>
       </c>
       <c r="D6" t="n">
-        <v>14.79999038294181</v>
+        <v>2.404998437228044</v>
       </c>
       <c r="E6" t="n">
-        <v>22.0040899680784</v>
+        <v>3.57566461981274</v>
       </c>
       <c r="F6" t="n">
-        <v>25.44277870537601</v>
+        <v>4.134451539623601</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.59371771750344</v>
+        <v>5.133979129094309</v>
       </c>
       <c r="D7" t="n">
-        <v>28.58213000922425</v>
+        <v>4.644596126498941</v>
       </c>
       <c r="E7" t="n">
-        <v>22.0040899680784</v>
+        <v>3.57566461981274</v>
       </c>
       <c r="F7" t="n">
-        <v>25.44277870537601</v>
+        <v>4.134451539623601</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>26.90673750239547</v>
+        <v>4.372344844139263</v>
       </c>
       <c r="D8" t="n">
-        <v>8.860022573334675</v>
+        <v>1.439753668166885</v>
       </c>
       <c r="E8" t="n">
-        <v>22.0040899680784</v>
+        <v>3.57566461981274</v>
       </c>
       <c r="F8" t="n">
-        <v>25.44277870537601</v>
+        <v>4.134451539623601</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>32.92351584611742</v>
+        <v>5.35007132499408</v>
       </c>
       <c r="D9" t="n">
-        <v>32.55141543200951</v>
+        <v>5.289605007701546</v>
       </c>
       <c r="E9" t="n">
-        <v>22.0040899680784</v>
+        <v>3.57566461981274</v>
       </c>
       <c r="F9" t="n">
-        <v>25.44277870537601</v>
+        <v>4.134451539623601</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>7.295189791157451</v>
+        <v>1.185468341063086</v>
       </c>
       <c r="D10" t="n">
-        <v>7.538353853012999</v>
+        <v>1.224982501114612</v>
       </c>
       <c r="E10" t="n">
-        <v>22.0040899680784</v>
+        <v>3.57566461981274</v>
       </c>
       <c r="F10" t="n">
-        <v>25.44277870537601</v>
+        <v>4.134451539623601</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>50.23419237120966</v>
+        <v>8.16305626032157</v>
       </c>
       <c r="D11" t="n">
-        <v>42.0212290181346</v>
+        <v>6.828449715446873</v>
       </c>
       <c r="E11" t="n">
-        <v>22.0040899680784</v>
+        <v>3.57566461981274</v>
       </c>
       <c r="F11" t="n">
-        <v>25.44277870537601</v>
+        <v>4.134451539623601</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>75.88791252780788</v>
+        <v>12.33178578576878</v>
       </c>
       <c r="D12" t="n">
-        <v>82.18992361223788</v>
+        <v>13.35586258698866</v>
       </c>
       <c r="E12" t="n">
-        <v>22.0040899680784</v>
+        <v>3.57566461981274</v>
       </c>
       <c r="F12" t="n">
-        <v>25.44277870537601</v>
+        <v>4.134451539623601</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>78.47912417222177</v>
+        <v>12.75285767798604</v>
       </c>
       <c r="D13" t="n">
-        <v>82.54523017832186</v>
+        <v>13.4135999039773</v>
       </c>
       <c r="E13" t="n">
-        <v>22.0040899680784</v>
+        <v>3.57566461981274</v>
       </c>
       <c r="F13" t="n">
-        <v>25.44277870537601</v>
+        <v>4.134451539623601</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
